--- a/Treinamento/IndexacaoFG/Arquivos/Recusa Sicoob 19.11.2025.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Recusa Sicoob 19.11.2025.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/thaiana_felipe_allianz_com_br/Documents/RECUSAS SICOOB/RECUSA/NOVEMBRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{9F761D16-8AD9-4E26-9236-DAD03C5702B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE9697F6-BFF4-452E-BAFB-21A06C21E624}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{9F761D16-8AD9-4E26-9236-DAD03C5702B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6199DEC-49A3-44A4-AE4B-779B1EBEE252}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{21DD7E13-A1D9-4F83-BEE2-A8D27A4EA0FA}"/>
   </bookViews>
   <sheets>
-    <sheet name="Recusa Sicoob 20.11.2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Recusa Sicoob 19.11.2025" sheetId="1" r:id="rId1"/>
     <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="40">
   <si>
     <t>RAMO</t>
   </si>
@@ -69,7 +69,94 @@
     <t>Falta de Vistoria</t>
   </si>
   <si>
-    <t>Vistoria Prévia Presencial Obrigatória.SEGURADO NÃO COMPARECEU NO POSTO FIXO.</t>
+    <t xml:space="preserve">MARIA ROSARIA DE JESUS FERNANDES SILVESTRE   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENATO ROBSON SODA                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AILTON GOMES DA SILVA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL TADEU DE ALMEIDA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RN SERVICOS E LOCACOES AGRICOLAS LTDA ME     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMILLY VICTORIA RODRIGUES SILVA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IGOR OLIVEIRA DE ALMEIDA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCOS JUSTINIANO DA SILVA                   </t>
+  </si>
+  <si>
+    <t>ASSOCIACAO DE ENSINO VALE DO GORUTUBA S S LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BERTOLINO JULIAO                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA ISLANDIA DA SILVA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELIAS SEBASTIAO RODRIGUES                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ MARIANO MACHADO FILHO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">	19/11/2025</t>
+  </si>
+  <si>
+    <t>Vistoria Prévia Presencial Obrigatória. SEGURADO NÃO COMPARECEU NO POSTO FIXO.</t>
+  </si>
+  <si>
+    <t>Caminhão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Vistoria Digital Obrigatória.	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Vistoria Prévia Presencial Obrigatória.</t>
+  </si>
+  <si>
+    <t>Vistoria Recusada</t>
+  </si>
+  <si>
+    <t>Moto</t>
+  </si>
+  <si>
+    <t>Bloqueio recusado devido ao parecer da vistoria prévia.VEICULO COM PLACA AVARIADA</t>
+  </si>
+  <si>
+    <t>Vida</t>
+  </si>
+  <si>
+    <t>Demais Motivos</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Indexação de Proposta</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Acúmulo de Risco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Vistoria Digital Obrigatória.</t>
+  </si>
+  <si>
+    <t>Vistoria Prévia Presencial Obrigatória.</t>
+  </si>
+  <si>
+    <t>Empresa</t>
+  </si>
+  <si>
+    <t>Falta Inspeção</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Inspeção de Risco</t>
   </si>
 </sst>
 </file>
@@ -136,7 +223,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -159,25 +246,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -193,42 +267,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -614,230 +677,448 @@
       </c>
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="7" t="s">
+      <c r="B2" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="11">
+        <v>45972</v>
+      </c>
+      <c r="D2" s="12">
+        <v>135352291</v>
+      </c>
+      <c r="E2" s="15">
+        <v>316579661</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="7" t="s">
-        <v>10</v>
+      <c r="H2" s="10" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A3" s="11"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
+      <c r="A3" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="11">
+        <v>45973</v>
+      </c>
+      <c r="D3" s="12">
+        <v>135370346</v>
+      </c>
+      <c r="E3" s="15">
+        <v>5766189699</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
+      <c r="A4" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="11">
+        <v>45975</v>
+      </c>
+      <c r="D4" s="12">
+        <v>135397882</v>
+      </c>
+      <c r="E4" s="15">
+        <v>37195417620</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
+      <c r="A5" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="11">
+        <v>45978</v>
+      </c>
+      <c r="D5" s="12">
+        <v>135419107</v>
+      </c>
+      <c r="E5" s="15">
+        <v>6999550689</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
+      <c r="A6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="11">
+        <v>45968</v>
+      </c>
+      <c r="D6" s="12">
+        <v>135309537</v>
+      </c>
+      <c r="E6" s="15">
+        <v>15274300000000</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
+      <c r="A7" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="11">
+        <v>45980</v>
+      </c>
+      <c r="D7" s="12">
+        <v>135475736</v>
+      </c>
+      <c r="E7" s="15">
+        <v>16979049631</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
+      <c r="A8" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="11">
+        <v>45974</v>
+      </c>
+      <c r="D8" s="12">
+        <v>135386173</v>
+      </c>
+      <c r="E8" s="15">
+        <v>12119283656</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
+      <c r="A9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="11">
+        <v>45699</v>
+      </c>
+      <c r="D9" s="12">
+        <v>131322144</v>
+      </c>
+      <c r="E9" s="15">
+        <v>11879460602</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
+      <c r="A10" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="11">
+        <v>45968</v>
+      </c>
+      <c r="D10" s="12">
+        <v>135308797</v>
+      </c>
+      <c r="E10" s="15">
+        <v>4463990000000</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
+      <c r="A11" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="13">
+        <v>45971</v>
+      </c>
+      <c r="D11" s="12">
+        <v>135325557</v>
+      </c>
+      <c r="E11" s="15">
+        <v>328265675</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="13"/>
+      <c r="A12" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="13">
+        <v>45971</v>
+      </c>
+      <c r="D12" s="12">
+        <v>135330994</v>
+      </c>
+      <c r="E12" s="15">
+        <v>6543798661</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="13"/>
+      <c r="A13" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="13">
+        <v>45973</v>
+      </c>
+      <c r="D13" s="12">
+        <v>135356620</v>
+      </c>
+      <c r="E13" s="15">
+        <v>25952729851</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="13"/>
+      <c r="A14" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="13">
+        <v>45973</v>
+      </c>
+      <c r="D14" s="12">
+        <v>135362184</v>
+      </c>
+      <c r="E14" s="15">
+        <v>71048790649</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" ht="13" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="13"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="18"/>
+      <c r="A15" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="13">
+        <v>45973</v>
+      </c>
+      <c r="D15" s="12">
+        <v>135362275</v>
+      </c>
+      <c r="E15" s="15">
+        <v>71048790649</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="16"/>
       <c r="G16" s="18"/>
-      <c r="H16" s="20"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="20"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="20"/>
+      <c r="H16" s="19"/>
+    </row>
+    <row r="17" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="19"/>
+    </row>
+    <row r="18" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="19"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="20"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="9"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="20"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="9"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="20"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="9"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="20"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="9"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="20"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="9"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1">
@@ -873,6 +1154,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
@@ -915,66 +1205,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac14f8cb44178d381f4c0afb30680a90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e58414b065c9b590c40efa77cd84bb6" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -1352,7 +1583,65 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BB309AC-A5CF-472C-9D2F-757AD536FA9A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22EF1522-EC78-49BD-B6F5-8B50F4C6CC13}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1364,23 +1653,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BB309AC-A5CF-472C-9D2F-757AD536FA9A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12F75303-5205-455D-B7DB-E1BE7757CE43}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF4E4C30-01AF-4BA7-A2CD-E239BE667D8B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1398,4 +1671,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12F75303-5205-455D-B7DB-E1BE7757CE43}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>